--- a/client/public/products/pack1-pm-essentials/pm-essentials-workbook.xlsx
+++ b/client/public/products/pack1-pm-essentials/pm-essentials-workbook.xlsx
@@ -27,14 +27,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="166" formatCode="$#,##0"/>
-    <numFmt numFmtId="167" formatCode="$#,##0;[Red]-$#,##0"/>
-    <numFmt numFmtId="168" formatCode="0%;[Red]-0%"/>
-    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="170" formatCode="mmm d, yyyy"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="mmm d, yyyy"/>
+    <numFmt numFmtId="165" formatCode="$#,##0"/>
+    <numFmt numFmtId="166" formatCode="$#,##0;[Red]-$#,##0"/>
+    <numFmt numFmtId="167" formatCode="0%;[Red]-0%"/>
+    <numFmt numFmtId="168" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="42">
     <font>
@@ -346,7 +344,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -397,11 +395,71 @@
         <color rgb="FFE5E7EB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -418,7 +476,7 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="11" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -434,7 +492,7 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="33" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="33" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -481,12 +539,12 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -535,7 +593,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -626,6 +684,34 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1288,7 +1374,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="89" t="n">
         <v>46280</v>
       </c>
     </row>
@@ -1342,7 +1428,7 @@
           <t>Budget Authority</t>
         </is>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="90">
         <f>'Spend Plan'!C7</f>
         <v/>
       </c>
@@ -1362,7 +1448,7 @@
           <t>Obligated to date</t>
         </is>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="90">
         <f>'Spend Plan'!C29</f>
         <v/>
       </c>
@@ -1427,7 +1513,7 @@
           <t>Remaining to Yr-1 goal</t>
         </is>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="90">
         <f>'Spend Plan'!C32</f>
         <v/>
       </c>
@@ -1451,15 +1537,24 @@
         <f t="array" ref="E16">_xlfn.TEXTJOIN(CHAR(10),TRUE,IF(('Risk Register'!$I$16:$I$31="HIGH")*('Risk Register'!$N$16:$N$31="Open"),'Risk Register'!$B$16:$B$31&amp;" "&amp;'Risk Register'!$C$16:$C$31,""))</f>
         <v/>
       </c>
+      <c r="F16" s="91" t="n"/>
       <c r="H16" s="15" t="inlineStr">
         <is>
           <t>FIRST 90 DAYS shows where you are in taking over the program. Below 50% on Orient after day 30 means you are still finding out things you should already know.</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
+    <row r="17">
+      <c r="E17" s="92" t="n"/>
+      <c r="F17" s="93" t="n"/>
+    </row>
+    <row r="18">
+      <c r="E18" s="92" t="n"/>
+      <c r="F18" s="93" t="n"/>
+    </row>
     <row r="19">
+      <c r="E19" s="94" t="n"/>
+      <c r="F19" s="95" t="n"/>
       <c r="H19" s="15" t="inlineStr">
         <is>
           <t>ACCOUNTABILITY is red if any decision in the RACI has no Accountable owner. That is the gap that turns into “I thought you had that.”</t>
@@ -2569,7 +2664,7 @@
           <t>Total Budget Authority</t>
         </is>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="96" t="n">
         <v>4150000</v>
       </c>
       <c r="I7" s="28" t="inlineStr">
@@ -2617,7 +2712,7 @@
           <t>Goal $ (Yr 1)</t>
         </is>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="97">
         <f>C7*C9</f>
         <v/>
       </c>
@@ -2690,25 +2785,25 @@
           <t>Oct</t>
         </is>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="96" t="n">
         <v>249000</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="96" t="n">
         <v>207500</v>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="97">
         <f>C13+0</f>
         <v/>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="97">
         <f>IF(D13="","",D13+N(0))</f>
         <v/>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="98">
         <f>IF(F13="","",F13-E13)</f>
         <v/>
       </c>
-      <c r="H13" s="38">
+      <c r="H13" s="99">
         <f>IF(F13="","",IF(E13=0,0,(F13-E13)/E13))</f>
         <v/>
       </c>
@@ -2716,17 +2811,17 @@
         <f>IF(F13="","",IF(H13&lt;-0.1,"BEHIND",IF(H13&gt;0.1,"AHEAD","ON PLAN")))</f>
         <v/>
       </c>
-      <c r="J13" s="35" t="n">
+      <c r="J13" s="96" t="n">
         <v>83000</v>
       </c>
-      <c r="K13" s="35" t="n">
+      <c r="K13" s="96" t="n">
         <v>83000</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="97">
         <f>J13+0</f>
         <v/>
       </c>
-      <c r="M13" s="36">
+      <c r="M13" s="97">
         <f>IF(K13="","",K13+N(0))</f>
         <v/>
       </c>
@@ -2737,25 +2832,25 @@
           <t>Nov</t>
         </is>
       </c>
-      <c r="C14" s="35" t="n">
+      <c r="C14" s="96" t="n">
         <v>332000</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="96" t="n">
         <v>290500</v>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="97">
         <f>C14+E13</f>
         <v/>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="97">
         <f>IF(D14="","",D14+N(F13))</f>
         <v/>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="98">
         <f>IF(F14="","",F14-E14)</f>
         <v/>
       </c>
-      <c r="H14" s="38">
+      <c r="H14" s="99">
         <f>IF(F14="","",IF(E14=0,0,(F14-E14)/E14))</f>
         <v/>
       </c>
@@ -2763,17 +2858,17 @@
         <f>IF(F14="","",IF(H14&lt;-0.1,"BEHIND",IF(H14&gt;0.1,"AHEAD","ON PLAN")))</f>
         <v/>
       </c>
-      <c r="J14" s="35" t="n">
+      <c r="J14" s="96" t="n">
         <v>166000</v>
       </c>
-      <c r="K14" s="35" t="n">
+      <c r="K14" s="96" t="n">
         <v>124500</v>
       </c>
-      <c r="L14" s="36">
+      <c r="L14" s="97">
         <f>J14+L13</f>
         <v/>
       </c>
-      <c r="M14" s="36">
+      <c r="M14" s="97">
         <f>IF(K14="","",K14+N(M13))</f>
         <v/>
       </c>
@@ -2784,25 +2879,25 @@
           <t>Dec</t>
         </is>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="96" t="n">
         <v>415000</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="96" t="n">
         <v>456500</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="97">
         <f>C15+E14</f>
         <v/>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="97">
         <f>IF(D15="","",D15+N(F14))</f>
         <v/>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="98">
         <f>IF(F15="","",F15-E15)</f>
         <v/>
       </c>
-      <c r="H15" s="38">
+      <c r="H15" s="99">
         <f>IF(F15="","",IF(E15=0,0,(F15-E15)/E15))</f>
         <v/>
       </c>
@@ -2810,17 +2905,17 @@
         <f>IF(F15="","",IF(H15&lt;-0.1,"BEHIND",IF(H15&gt;0.1,"AHEAD","ON PLAN")))</f>
         <v/>
       </c>
-      <c r="J15" s="35" t="n">
+      <c r="J15" s="96" t="n">
         <v>249000</v>
       </c>
-      <c r="K15" s="35" t="n">
+      <c r="K15" s="96" t="n">
         <v>207500</v>
       </c>
-      <c r="L15" s="36">
+      <c r="L15" s="97">
         <f>J15+L14</f>
         <v/>
       </c>
-      <c r="M15" s="36">
+      <c r="M15" s="97">
         <f>IF(K15="","",K15+N(M14))</f>
         <v/>
       </c>
@@ -2831,25 +2926,25 @@
           <t>Jan</t>
         </is>
       </c>
-      <c r="C16" s="35" t="n">
+      <c r="C16" s="96" t="n">
         <v>373500</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="96" t="n">
         <v>332000</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="97">
         <f>C16+E15</f>
         <v/>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="97">
         <f>IF(D16="","",D16+N(F15))</f>
         <v/>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="98">
         <f>IF(F16="","",F16-E16)</f>
         <v/>
       </c>
-      <c r="H16" s="38">
+      <c r="H16" s="99">
         <f>IF(F16="","",IF(E16=0,0,(F16-E16)/E16))</f>
         <v/>
       </c>
@@ -2857,17 +2952,17 @@
         <f>IF(F16="","",IF(H16&lt;-0.1,"BEHIND",IF(H16&gt;0.1,"AHEAD","ON PLAN")))</f>
         <v/>
       </c>
-      <c r="J16" s="35" t="n">
+      <c r="J16" s="96" t="n">
         <v>332000</v>
       </c>
-      <c r="K16" s="35" t="n">
+      <c r="K16" s="96" t="n">
         <v>290500</v>
       </c>
-      <c r="L16" s="36">
+      <c r="L16" s="97">
         <f>J16+L15</f>
         <v/>
       </c>
-      <c r="M16" s="36">
+      <c r="M16" s="97">
         <f>IF(K16="","",K16+N(M15))</f>
         <v/>
       </c>
@@ -2878,25 +2973,25 @@
           <t>Feb</t>
         </is>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="96" t="n">
         <v>373500</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="96" t="n">
         <v>415000</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="97">
         <f>C17+E16</f>
         <v/>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="97">
         <f>IF(D17="","",D17+N(F16))</f>
         <v/>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="98">
         <f>IF(F17="","",F17-E17)</f>
         <v/>
       </c>
-      <c r="H17" s="38">
+      <c r="H17" s="99">
         <f>IF(F17="","",IF(E17=0,0,(F17-E17)/E17))</f>
         <v/>
       </c>
@@ -2904,17 +2999,17 @@
         <f>IF(F17="","",IF(H17&lt;-0.1,"BEHIND",IF(H17&gt;0.1,"AHEAD","ON PLAN")))</f>
         <v/>
       </c>
-      <c r="J17" s="35" t="n">
+      <c r="J17" s="96" t="n">
         <v>373500</v>
       </c>
-      <c r="K17" s="35" t="n">
+      <c r="K17" s="96" t="n">
         <v>373500</v>
       </c>
-      <c r="L17" s="36">
+      <c r="L17" s="97">
         <f>J17+L16</f>
         <v/>
       </c>
-      <c r="M17" s="36">
+      <c r="M17" s="97">
         <f>IF(K17="","",K17+N(M16))</f>
         <v/>
       </c>
@@ -2925,25 +3020,25 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="96" t="n">
         <v>373500</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="96" t="n">
         <v>332000</v>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="97">
         <f>C18+E17</f>
         <v/>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="97">
         <f>IF(D18="","",D18+N(F17))</f>
         <v/>
       </c>
-      <c r="G18" s="37">
+      <c r="G18" s="98">
         <f>IF(F18="","",F18-E18)</f>
         <v/>
       </c>
-      <c r="H18" s="38">
+      <c r="H18" s="99">
         <f>IF(F18="","",IF(E18=0,0,(F18-E18)/E18))</f>
         <v/>
       </c>
@@ -2951,17 +3046,17 @@
         <f>IF(F18="","",IF(H18&lt;-0.1,"BEHIND",IF(H18&gt;0.1,"AHEAD","ON PLAN")))</f>
         <v/>
       </c>
-      <c r="J18" s="35" t="n">
+      <c r="J18" s="96" t="n">
         <v>415000</v>
       </c>
-      <c r="K18" s="35" t="n">
+      <c r="K18" s="96" t="n">
         <v>373500</v>
       </c>
-      <c r="L18" s="36">
+      <c r="L18" s="97">
         <f>J18+L17</f>
         <v/>
       </c>
-      <c r="M18" s="36">
+      <c r="M18" s="97">
         <f>IF(K18="","",K18+N(M17))</f>
         <v/>
       </c>
@@ -2972,23 +3067,23 @@
           <t>Apr</t>
         </is>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="96" t="n">
         <v>373500</v>
       </c>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="36">
+      <c r="D19" s="96" t="n"/>
+      <c r="E19" s="97">
         <f>C19+E18</f>
         <v/>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="97">
         <f>IF(D19="","",D19+N(F18))</f>
         <v/>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="98">
         <f>IF(F19="","",F19-E19)</f>
         <v/>
       </c>
-      <c r="H19" s="38">
+      <c r="H19" s="99">
         <f>IF(F19="","",IF(E19=0,0,(F19-E19)/E19))</f>
         <v/>
       </c>
@@ -2996,15 +3091,15 @@
         <f>IF(F19="","",IF(H19&lt;-0.1,"BEHIND",IF(H19&gt;0.1,"AHEAD","ON PLAN")))</f>
         <v/>
       </c>
-      <c r="J19" s="35" t="n">
+      <c r="J19" s="96" t="n">
         <v>415000</v>
       </c>
-      <c r="K19" s="35" t="n"/>
-      <c r="L19" s="36">
+      <c r="K19" s="96" t="n"/>
+      <c r="L19" s="97">
         <f>J19+L18</f>
         <v/>
       </c>
-      <c r="M19" s="36">
+      <c r="M19" s="97">
         <f>IF(K19="","",K19+N(M18))</f>
         <v/>
       </c>
@@ -3015,23 +3110,23 @@
           <t>May</t>
         </is>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="96" t="n">
         <v>373500</v>
       </c>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="36">
+      <c r="D20" s="96" t="n"/>
+      <c r="E20" s="97">
         <f>C20+E19</f>
         <v/>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="97">
         <f>IF(D20="","",D20+N(F19))</f>
         <v/>
       </c>
-      <c r="G20" s="37">
+      <c r="G20" s="98">
         <f>IF(F20="","",F20-E20)</f>
         <v/>
       </c>
-      <c r="H20" s="38">
+      <c r="H20" s="99">
         <f>IF(F20="","",IF(E20=0,0,(F20-E20)/E20))</f>
         <v/>
       </c>
@@ -3039,15 +3134,15 @@
         <f>IF(F20="","",IF(H20&lt;-0.1,"BEHIND",IF(H20&gt;0.1,"AHEAD","ON PLAN")))</f>
         <v/>
       </c>
-      <c r="J20" s="35" t="n">
+      <c r="J20" s="96" t="n">
         <v>415000</v>
       </c>
-      <c r="K20" s="35" t="n"/>
-      <c r="L20" s="36">
+      <c r="K20" s="96" t="n"/>
+      <c r="L20" s="97">
         <f>J20+L19</f>
         <v/>
       </c>
-      <c r="M20" s="36">
+      <c r="M20" s="97">
         <f>IF(K20="","",K20+N(M19))</f>
         <v/>
       </c>
@@ -3058,23 +3153,23 @@
           <t>Jun</t>
         </is>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="96" t="n">
         <v>373500</v>
       </c>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="36">
+      <c r="D21" s="96" t="n"/>
+      <c r="E21" s="97">
         <f>C21+E20</f>
         <v/>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="97">
         <f>IF(D21="","",D21+N(F20))</f>
         <v/>
       </c>
-      <c r="G21" s="37">
+      <c r="G21" s="98">
         <f>IF(F21="","",F21-E21)</f>
         <v/>
       </c>
-      <c r="H21" s="38">
+      <c r="H21" s="99">
         <f>IF(F21="","",IF(E21=0,0,(F21-E21)/E21))</f>
         <v/>
       </c>
@@ -3082,15 +3177,15 @@
         <f>IF(F21="","",IF(H21&lt;-0.1,"BEHIND",IF(H21&gt;0.1,"AHEAD","ON PLAN")))</f>
         <v/>
       </c>
-      <c r="J21" s="35" t="n">
+      <c r="J21" s="96" t="n">
         <v>415000</v>
       </c>
-      <c r="K21" s="35" t="n"/>
-      <c r="L21" s="36">
+      <c r="K21" s="96" t="n"/>
+      <c r="L21" s="97">
         <f>J21+L20</f>
         <v/>
       </c>
-      <c r="M21" s="36">
+      <c r="M21" s="97">
         <f>IF(K21="","",K21+N(M20))</f>
         <v/>
       </c>
@@ -3101,23 +3196,23 @@
           <t>Jul</t>
         </is>
       </c>
-      <c r="C22" s="35" t="n">
+      <c r="C22" s="96" t="n">
         <v>332000</v>
       </c>
-      <c r="D22" s="35" t="n"/>
-      <c r="E22" s="36">
+      <c r="D22" s="96" t="n"/>
+      <c r="E22" s="97">
         <f>C22+E21</f>
         <v/>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="97">
         <f>IF(D22="","",D22+N(F21))</f>
         <v/>
       </c>
-      <c r="G22" s="37">
+      <c r="G22" s="98">
         <f>IF(F22="","",F22-E22)</f>
         <v/>
       </c>
-      <c r="H22" s="38">
+      <c r="H22" s="99">
         <f>IF(F22="","",IF(E22=0,0,(F22-E22)/E22))</f>
         <v/>
       </c>
@@ -3125,15 +3220,15 @@
         <f>IF(F22="","",IF(H22&lt;-0.1,"BEHIND",IF(H22&gt;0.1,"AHEAD","ON PLAN")))</f>
         <v/>
       </c>
-      <c r="J22" s="35" t="n">
+      <c r="J22" s="96" t="n">
         <v>415000</v>
       </c>
-      <c r="K22" s="35" t="n"/>
-      <c r="L22" s="36">
+      <c r="K22" s="96" t="n"/>
+      <c r="L22" s="97">
         <f>J22+L21</f>
         <v/>
       </c>
-      <c r="M22" s="36">
+      <c r="M22" s="97">
         <f>IF(K22="","",K22+N(M21))</f>
         <v/>
       </c>
@@ -3144,23 +3239,23 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="C23" s="35" t="n">
+      <c r="C23" s="96" t="n">
         <v>290500</v>
       </c>
-      <c r="D23" s="35" t="n"/>
-      <c r="E23" s="36">
+      <c r="D23" s="96" t="n"/>
+      <c r="E23" s="97">
         <f>C23+E22</f>
         <v/>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="97">
         <f>IF(D23="","",D23+N(F22))</f>
         <v/>
       </c>
-      <c r="G23" s="37">
+      <c r="G23" s="98">
         <f>IF(F23="","",F23-E23)</f>
         <v/>
       </c>
-      <c r="H23" s="38">
+      <c r="H23" s="99">
         <f>IF(F23="","",IF(E23=0,0,(F23-E23)/E23))</f>
         <v/>
       </c>
@@ -3168,15 +3263,15 @@
         <f>IF(F23="","",IF(H23&lt;-0.1,"BEHIND",IF(H23&gt;0.1,"AHEAD","ON PLAN")))</f>
         <v/>
       </c>
-      <c r="J23" s="35" t="n">
+      <c r="J23" s="96" t="n">
         <v>456500</v>
       </c>
-      <c r="K23" s="35" t="n"/>
-      <c r="L23" s="36">
+      <c r="K23" s="96" t="n"/>
+      <c r="L23" s="97">
         <f>J23+L22</f>
         <v/>
       </c>
-      <c r="M23" s="36">
+      <c r="M23" s="97">
         <f>IF(K23="","",K23+N(M22))</f>
         <v/>
       </c>
@@ -3187,23 +3282,23 @@
           <t>Sep</t>
         </is>
       </c>
-      <c r="C24" s="35" t="n">
+      <c r="C24" s="96" t="n">
         <v>290500</v>
       </c>
-      <c r="D24" s="35" t="n"/>
-      <c r="E24" s="36">
+      <c r="D24" s="96" t="n"/>
+      <c r="E24" s="97">
         <f>C24+E23</f>
         <v/>
       </c>
-      <c r="F24" s="36">
+      <c r="F24" s="97">
         <f>IF(D24="","",D24+N(F23))</f>
         <v/>
       </c>
-      <c r="G24" s="37">
+      <c r="G24" s="98">
         <f>IF(F24="","",F24-E24)</f>
         <v/>
       </c>
-      <c r="H24" s="38">
+      <c r="H24" s="99">
         <f>IF(F24="","",IF(E24=0,0,(F24-E24)/E24))</f>
         <v/>
       </c>
@@ -3211,15 +3306,15 @@
         <f>IF(F24="","",IF(H24&lt;-0.1,"BEHIND",IF(H24&gt;0.1,"AHEAD","ON PLAN")))</f>
         <v/>
       </c>
-      <c r="J24" s="35" t="n">
+      <c r="J24" s="96" t="n">
         <v>415000</v>
       </c>
-      <c r="K24" s="35" t="n"/>
-      <c r="L24" s="36">
+      <c r="K24" s="96" t="n"/>
+      <c r="L24" s="97">
         <f>J24+L23</f>
         <v/>
       </c>
-      <c r="M24" s="36">
+      <c r="M24" s="97">
         <f>IF(K24="","",K24+N(M23))</f>
         <v/>
       </c>
@@ -3248,7 +3343,7 @@
           <t>Planned to date</t>
         </is>
       </c>
-      <c r="C28" s="36">
+      <c r="C28" s="97">
         <f>IF(C27=0,0,INDEX(E13:E24,C27))</f>
         <v/>
       </c>
@@ -3259,7 +3354,7 @@
           <t>Obligated to date</t>
         </is>
       </c>
-      <c r="C29" s="36">
+      <c r="C29" s="97">
         <f>IF(C27=0,0,INDEX(F13:F24,C27))</f>
         <v/>
       </c>
@@ -3292,7 +3387,7 @@
           <t>Remaining to Yr-1 goal</t>
         </is>
       </c>
-      <c r="C32" s="36">
+      <c r="C32" s="97">
         <f>MAX(0,C10-C29)</f>
         <v/>
       </c>
@@ -3303,7 +3398,7 @@
           <t>Expended to date</t>
         </is>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="97">
         <f>IF(C27=0,0,INDEX(M13:M24,C27))</f>
         <v/>
       </c>
@@ -3370,7 +3465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="B2:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3380,6 +3475,8 @@
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="35" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -3388,7 +3485,6 @@
     <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="30" customHeight="1">
       <c r="B2" s="43" t="inlineStr">
         <is>
@@ -3403,7 +3499,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1">
       <c r="B5" s="45" t="inlineStr">
         <is>
@@ -3546,17 +3641,99 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
+    <row r="13">
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="42" t="inlineStr">
+        <is>
+          <t>Change Probability and Impact (1–5) for your program. Score, Level, the Risk Map, and the Dashboard update themselves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="100" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C15" s="100" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="D15" s="100" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E15" s="100" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F15" s="100" t="inlineStr">
+        <is>
+          <t>Probability (1–5)</t>
+        </is>
+      </c>
+      <c r="G15" s="100" t="inlineStr">
+        <is>
+          <t>Impact (1–5)</t>
+        </is>
+      </c>
+      <c r="H15" s="100" t="inlineStr">
+        <is>
+          <t>Score (P×I)</t>
+        </is>
+      </c>
+      <c r="I15" s="100" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="J15" s="100" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+      <c r="K15" s="100" t="inlineStr">
+        <is>
+          <t>Contingency</t>
+        </is>
+      </c>
+      <c r="L15" s="100" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="M15" s="100" t="inlineStr">
+        <is>
+          <t>Target Date</t>
+        </is>
+      </c>
+      <c r="N15" s="100" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="O15" s="100" t="inlineStr">
+        <is>
+          <t>Date Identified</t>
+        </is>
+      </c>
+    </row>
     <row r="16" ht="49.5" customHeight="1">
       <c r="B16" s="52" t="inlineStr">
         <is>
           <t>R-001</t>
         </is>
       </c>
-      <c r="C16" s="53" t="inlineStr">
+      <c r="C16" s="102" t="inlineStr">
         <is>
           <t>Software Integration Failure</t>
         </is>
@@ -3600,7 +3777,7 @@
           <t>Systems Engineer</t>
         </is>
       </c>
-      <c r="M16" s="56" t="n">
+      <c r="M16" s="101" t="n">
         <v>46134</v>
       </c>
       <c r="N16" s="52" t="inlineStr">
@@ -3608,7 +3785,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="O16" s="56" t="n">
+      <c r="O16" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -3618,7 +3795,7 @@
           <t>R-002</t>
         </is>
       </c>
-      <c r="C17" s="53" t="inlineStr">
+      <c r="C17" s="102" t="inlineStr">
         <is>
           <t>Key Personnel Departure</t>
         </is>
@@ -3662,7 +3839,7 @@
           <t>HR Director</t>
         </is>
       </c>
-      <c r="M17" s="56" t="n">
+      <c r="M17" s="101" t="n">
         <v>46164</v>
       </c>
       <c r="N17" s="52" t="inlineStr">
@@ -3670,7 +3847,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="O17" s="56" t="n">
+      <c r="O17" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -3680,7 +3857,7 @@
           <t>R-003</t>
         </is>
       </c>
-      <c r="C18" s="53" t="inlineStr">
+      <c r="C18" s="102" t="inlineStr">
         <is>
           <t>Requirements Creep</t>
         </is>
@@ -3724,7 +3901,7 @@
           <t>PM</t>
         </is>
       </c>
-      <c r="M18" s="56" t="n">
+      <c r="M18" s="101" t="n">
         <v>46149</v>
       </c>
       <c r="N18" s="52" t="inlineStr">
@@ -3732,7 +3909,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="O18" s="56" t="n">
+      <c r="O18" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -3742,7 +3919,7 @@
           <t>R-004</t>
         </is>
       </c>
-      <c r="C19" s="53" t="inlineStr">
+      <c r="C19" s="102" t="inlineStr">
         <is>
           <t>Funding Shortfall / CR Impact</t>
         </is>
@@ -3786,7 +3963,7 @@
           <t>Finance Director</t>
         </is>
       </c>
-      <c r="M19" s="56" t="n">
+      <c r="M19" s="101" t="n">
         <v>46194</v>
       </c>
       <c r="N19" s="52" t="inlineStr">
@@ -3794,7 +3971,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="O19" s="56" t="n">
+      <c r="O19" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -3804,7 +3981,7 @@
           <t>R-005</t>
         </is>
       </c>
-      <c r="C20" s="53" t="inlineStr">
+      <c r="C20" s="102" t="inlineStr">
         <is>
           <t>Subcontractor Performance</t>
         </is>
@@ -3848,7 +4025,7 @@
           <t>Subcontracts Mgr</t>
         </is>
       </c>
-      <c r="M20" s="56" t="n">
+      <c r="M20" s="101" t="n">
         <v>46134</v>
       </c>
       <c r="N20" s="52" t="inlineStr">
@@ -3856,7 +4033,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="O20" s="56" t="n">
+      <c r="O20" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -3866,7 +4043,7 @@
           <t>R-006</t>
         </is>
       </c>
-      <c r="C21" s="53" t="inlineStr">
+      <c r="C21" s="102" t="inlineStr">
         <is>
           <t>CMMC Certification Delay</t>
         </is>
@@ -3910,7 +4087,7 @@
           <t>ISSM</t>
         </is>
       </c>
-      <c r="M21" s="56" t="n">
+      <c r="M21" s="101" t="n">
         <v>46224</v>
       </c>
       <c r="N21" s="52" t="inlineStr">
@@ -3918,7 +4095,7 @@
           <t>Mitigated</t>
         </is>
       </c>
-      <c r="O21" s="56" t="n">
+      <c r="O21" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -3928,7 +4105,7 @@
           <t>R-007</t>
         </is>
       </c>
-      <c r="C22" s="53" t="inlineStr">
+      <c r="C22" s="102" t="inlineStr">
         <is>
           <t>Test Environment Unavailability</t>
         </is>
@@ -3972,7 +4149,7 @@
           <t>Test Director</t>
         </is>
       </c>
-      <c r="M22" s="56" t="n">
+      <c r="M22" s="101" t="n">
         <v>46149</v>
       </c>
       <c r="N22" s="52" t="inlineStr">
@@ -3980,7 +4157,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="O22" s="56" t="n">
+      <c r="O22" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -3990,7 +4167,7 @@
           <t>R-008</t>
         </is>
       </c>
-      <c r="C23" s="53" t="inlineStr">
+      <c r="C23" s="102" t="inlineStr">
         <is>
           <t>Data Rights Dispute</t>
         </is>
@@ -4034,7 +4211,7 @@
           <t>Legal Counsel</t>
         </is>
       </c>
-      <c r="M23" s="56" t="n">
+      <c r="M23" s="101" t="n">
         <v>46164</v>
       </c>
       <c r="N23" s="52" t="inlineStr">
@@ -4042,7 +4219,7 @@
           <t>Accepted</t>
         </is>
       </c>
-      <c r="O23" s="56" t="n">
+      <c r="O23" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -4052,7 +4229,7 @@
           <t>R-009</t>
         </is>
       </c>
-      <c r="C24" s="53" t="inlineStr">
+      <c r="C24" s="102" t="inlineStr">
         <is>
           <t>EVM Compliance Gaps</t>
         </is>
@@ -4096,7 +4273,7 @@
           <t>Finance Director</t>
         </is>
       </c>
-      <c r="M24" s="56" t="n">
+      <c r="M24" s="101" t="n">
         <v>46134</v>
       </c>
       <c r="N24" s="52" t="inlineStr">
@@ -4104,7 +4281,7 @@
           <t>Mitigated</t>
         </is>
       </c>
-      <c r="O24" s="56" t="n">
+      <c r="O24" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -4114,7 +4291,7 @@
           <t>R-010</t>
         </is>
       </c>
-      <c r="C25" s="53" t="inlineStr">
+      <c r="C25" s="102" t="inlineStr">
         <is>
           <t>Supply Chain Disruption</t>
         </is>
@@ -4158,7 +4335,7 @@
           <t>Logistics Mgr</t>
         </is>
       </c>
-      <c r="M25" s="56" t="n">
+      <c r="M25" s="101" t="n">
         <v>46119</v>
       </c>
       <c r="N25" s="52" t="inlineStr">
@@ -4166,7 +4343,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="O25" s="56" t="n">
+      <c r="O25" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -4176,7 +4353,7 @@
           <t>R-011</t>
         </is>
       </c>
-      <c r="C26" s="53" t="inlineStr">
+      <c r="C26" s="102" t="inlineStr">
         <is>
           <t>Clearance Processing Delays</t>
         </is>
@@ -4220,7 +4397,7 @@
           <t>FSO</t>
         </is>
       </c>
-      <c r="M26" s="56" t="n">
+      <c r="M26" s="101" t="n">
         <v>46134</v>
       </c>
       <c r="N26" s="52" t="inlineStr">
@@ -4228,7 +4405,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="O26" s="56" t="n">
+      <c r="O26" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -4238,7 +4415,7 @@
           <t>R-012</t>
         </is>
       </c>
-      <c r="C27" s="53" t="inlineStr">
+      <c r="C27" s="102" t="inlineStr">
         <is>
           <t>Technical Debt Accumulation</t>
         </is>
@@ -4282,7 +4459,7 @@
           <t>Tech Lead</t>
         </is>
       </c>
-      <c r="M27" s="56" t="n">
+      <c r="M27" s="101" t="n">
         <v>46164</v>
       </c>
       <c r="N27" s="52" t="inlineStr">
@@ -4290,7 +4467,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="O27" s="56" t="n">
+      <c r="O27" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -4300,7 +4477,7 @@
           <t>R-013</t>
         </is>
       </c>
-      <c r="C28" s="53" t="inlineStr">
+      <c r="C28" s="102" t="inlineStr">
         <is>
           <t>Government Stakeholder Turnover</t>
         </is>
@@ -4344,7 +4521,7 @@
           <t>PM</t>
         </is>
       </c>
-      <c r="M28" s="56" t="n">
+      <c r="M28" s="101" t="n">
         <v>46194</v>
       </c>
       <c r="N28" s="52" t="inlineStr">
@@ -4352,7 +4529,7 @@
           <t>Accepted</t>
         </is>
       </c>
-      <c r="O28" s="56" t="n">
+      <c r="O28" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -4362,7 +4539,7 @@
           <t>R-014</t>
         </is>
       </c>
-      <c r="C29" s="53" t="inlineStr">
+      <c r="C29" s="102" t="inlineStr">
         <is>
           <t>Protest Delays Contract Start</t>
         </is>
@@ -4406,7 +4583,7 @@
           <t>PM</t>
         </is>
       </c>
-      <c r="M29" s="56" t="n">
+      <c r="M29" s="101" t="n">
         <v>46119</v>
       </c>
       <c r="N29" s="52" t="inlineStr">
@@ -4414,7 +4591,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="O29" s="56" t="n">
+      <c r="O29" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -4424,7 +4601,7 @@
           <t>R-015</t>
         </is>
       </c>
-      <c r="C30" s="53" t="inlineStr">
+      <c r="C30" s="102" t="inlineStr">
         <is>
           <t>Nunn-McCurdy Breach Risk</t>
         </is>
@@ -4468,7 +4645,7 @@
           <t>Finance Director</t>
         </is>
       </c>
-      <c r="M30" s="56" t="n">
+      <c r="M30" s="101" t="n">
         <v>46194</v>
       </c>
       <c r="N30" s="52" t="inlineStr">
@@ -4476,7 +4653,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="O30" s="56" t="n">
+      <c r="O30" s="101" t="n">
         <v>46104</v>
       </c>
     </row>
@@ -4486,7 +4663,7 @@
           <t>R-016</t>
         </is>
       </c>
-      <c r="C31" s="53" t="inlineStr">
+      <c r="C31" s="102" t="inlineStr">
         <is>
           <t>CMMC Level 2 Non-Compliance</t>
         </is>
@@ -4530,7 +4707,7 @@
           <t>Subcontracts Mgr</t>
         </is>
       </c>
-      <c r="M31" s="56" t="n">
+      <c r="M31" s="101" t="n">
         <v>46296</v>
       </c>
       <c r="N31" s="52" t="inlineStr">
@@ -4538,11 +4715,10 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="O31" s="56" t="n">
+      <c r="O31" s="101" t="n">
         <v>46266</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33" ht="15" customHeight="1">
       <c r="B33" s="57" t="n"/>
     </row>
@@ -4608,7 +4784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="B2:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4620,7 +4796,6 @@
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="30" customHeight="1">
       <c r="B2" s="59" t="inlineStr">
         <is>
@@ -4635,7 +4810,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1">
       <c r="B5" s="60" t="inlineStr">
         <is>
@@ -4778,8 +4952,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
     <row r="13" ht="15" customHeight="1">
       <c r="B13" s="45" t="inlineStr">
         <is>
@@ -4823,8 +4995,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
     <row r="19" ht="15" customHeight="1">
       <c r="B19" s="57" t="inlineStr">
         <is>
@@ -4832,8 +5002,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22">
       <c r="B22" s="69" t="inlineStr">
         <is>
@@ -4848,7 +5016,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="B25" s="70" t="inlineStr">
         <is>
@@ -5016,8 +5183,6 @@
         <v/>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33">
       <c r="B33" s="76" t="inlineStr">
         <is>
@@ -5025,7 +5190,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="B35" s="11" t="inlineStr">
         <is>
@@ -5061,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="B2:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -5072,7 +5236,6 @@
     <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="22" t="inlineStr">
         <is>
@@ -5087,7 +5250,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="77" t="inlineStr">
         <is>
@@ -5812,7 +5974,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="B34" s="21" t="inlineStr">
         <is>
@@ -5845,13 +6006,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="B2:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="86" t="inlineStr">
         <is>
@@ -6073,7 +6233,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
         <is>

--- a/client/public/products/pack1-pm-essentials/pm-essentials-workbook.xlsx
+++ b/client/public/products/pack1-pm-essentials/pm-essentials-workbook.xlsx
@@ -1284,7 +1284,7 @@
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Thresholds reflect FAC 2025-06 (SAT $350K, MPT $15K, effective Oct 1, 2025) and CMMC Phase 2 (C3PAO assessment required for Level 2, effective Nov 10, 2026). When these move, buyers get the updated file by email.</t>
+          <t>Thresholds reflect FAC 2025-06 (SAT $350K, MPT $15K, effective Oct 1, 2025), EVM at $50M and a validated EVMS at $100M (DFARS class deviation 2026-O0011), and CMMC as of September 2026: Phase 1 self-assessments are in contracts; Phase 2 third-party (C3PAO) assessments were suspended July 13, 2026 with no new date. When these move we update the file, and your download link always serves the current edition.</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>Verify CMMC / CUI posture on every contract handling CUI. Phase 2 (Nov 10, 2026) requires C3PAO assessment for Level 2.</t>
+          <t>Verify CMMC on every contract handling FCI or CUI: the required level, and a current status posted in SPRS for the contractor and each covered sub. Phase 2 C3PAO assessments are suspended (July 2026); check for a new date before you plan around one.</t>
         </is>
       </c>
       <c r="D14" s="26" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C19" s="29" t="inlineStr">
         <is>
-          <t>If EVM applies (&gt;$20M cost-type), review CPI and SPI trends and the contractor’s VAC. Ask what changed since last CPR.</t>
+          <t>If EVM applies ($50M and up on cost or incentive contracts; validated EVMS at $100M, DFARS class deviation 2026-O0011), review CPI and SPI trends and the contractor’s VAC. Ask what changed since the last report.</t>
         </is>
       </c>
       <c r="D19" s="30" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="C21" s="102" t="inlineStr">
         <is>
-          <t>CMMC Certification Delay</t>
+          <t>CMMC Requirements Change</t>
         </is>
       </c>
       <c r="D21" s="52" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>CMMC Phase 1 (self-assessment, Level 2) is active as of Nov 10, 2025. Phase 2 requires a C3PAO third-party assessment, mandatory by Nov 10, 2026. Organization must complete C3PAO assessment before Phase 2 deadline to remain eligible for DoD contracts involving CUI.</t>
+          <t>CMMC Phase 1 (self-assessments) has been in contracts since Nov 10, 2025. Phase 2 (C3PAO certification for Level 2) was suspended July 13, 2026 pending a DoD reform review, with no new date. The program is exposed if third-party assessments return mid-contract, or if a contractor's SPRS self-assessment does not hold up.</t>
         </is>
       </c>
       <c r="F21" s="52" t="n">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="J21" s="54" t="inlineStr">
         <is>
-          <t>Complete CMMC Level 2 self-assessment (Phase 1) immediately; remediate any POA&amp;M gaps. Engage accredited C3PAO assessor NLT Q1 2026 to schedule Phase 2 assessment before the Nov 10, 2026 mandatory deadline. Track via CMMC AB Marketplace.</t>
+          <t>Confirm each contract's required CMMC level and that current status is posted in SPRS; close any POA&amp;M items inside the 180-day window. Track the reform review and the next DFARS change. Keep a C3PAO readiness plan on the shelf, not on the schedule.</t>
         </is>
       </c>
       <c r="K21" s="54" t="inlineStr">
         <is>
-          <t>If C3PAO assessment cannot be completed before Nov 10, 2026, consult CO on contract impact and explore interim authorization options; ensure SPRS score reflects current NIST 800-171 implementation posture.</t>
+          <t>If a new Phase 2 date lands inside the period of performance, brief the CO on schedule and cost impact and price assessments into the next option or mod. Make sure SPRS scores reflect current NIST SP 800-171 implementation.</t>
         </is>
       </c>
       <c r="L21" s="52" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="E31" s="54" t="inlineStr">
         <is>
-          <t>Subcontractors handling Controlled Unclassified Information (CUI) may not complete required C3PAO third-party assessment before CMMC Phase 2 takes effect Nov 10, 2026, risking their eligibility to remain on contract</t>
+          <t>Subcontractors handling FCI or CUI may not have a current CMMC status in SPRS at the required level. The prime must flow down DFARS 252.204-7021 and confirm sub status before award; a sub that falls out of status puts CUI-handling work at risk.</t>
         </is>
       </c>
       <c r="F31" s="52" t="n">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="J31" s="54" t="inlineStr">
         <is>
-          <t>Confirm CMMC Level 2 self-assessment status for every subcontractor handling CUI now; require proof of scheduled C3PAO assessment; fund the assessment cost through a subcontract modification if needed</t>
+          <t>Confirm current CMMC status in SPRS for every subcontractor handling FCI or CUI; get POA&amp;M closeout dates in writing; budget for a C3PAO assessment in case the Phase 2 suspension ends.</t>
         </is>
       </c>
       <c r="K31" s="54" t="inlineStr">
         <is>
-          <t>Pre-qualify an alternate subcontractor already holding current CMMC Level 2 certification; be ready to transition CUI-handling work on short notice</t>
+          <t>Pre-qualify an alternate subcontractor with a current CMMC status at the required level; be ready to transition CUI-handling work on short notice.</t>
         </is>
       </c>
       <c r="L31" s="52" t="inlineStr">
